--- a/corr_matrix/residual_exam2B_3PL.xlsx
+++ b/corr_matrix/residual_exam2B_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2B01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03820855102680605</v>
+        <v>-0.03820050468191769</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1036790071198187</v>
+        <v>-0.1036926138894342</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.331089797631131</v>
+        <v>-0.3310883313074113</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.255029386532689</v>
+        <v>-0.2550368089498125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07542813836845864</v>
+        <v>0.07542806459283666</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02684651374004561</v>
+        <v>-0.02684996797353705</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04727185076144911</v>
+        <v>-0.04729886021489226</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02377053359026614</v>
+        <v>0.02376324638262087</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1225880484765356</v>
+        <v>0.1225047075877247</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01712310662967702</v>
+        <v>-0.017206840120118</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07721829699917829</v>
+        <v>-0.07723501618661995</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0614084395377903</v>
+        <v>-0.06147912687081618</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.06651761356820789</v>
+        <v>-0.0670025133674968</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1678714244500708</v>
+        <v>-0.1678669812375583</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2244993377801551</v>
+        <v>-0.2245020759487839</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.03820855102680605</v>
+        <v>-0.03820050468191769</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01234068078596404</v>
+        <v>0.01232275203338851</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2417226331508232</v>
+        <v>-0.2417254208296967</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07805718404123538</v>
+        <v>-0.07806354154150265</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.07455814137305526</v>
+        <v>-0.07455940277080558</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04508095526637061</v>
+        <v>-0.04508331966969938</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1499586067160359</v>
+        <v>-0.1499654042051256</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1114870266090247</v>
+        <v>0.111478058465224</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2443402950117502</v>
+        <v>-0.2444970228166385</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07431393497876562</v>
+        <v>0.0741899723638027</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1943296300502239</v>
+        <v>-0.194346715167301</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04310953272963792</v>
+        <v>0.04306455602606929</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.05767715707518035</v>
+        <v>-0.05820917583237969</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1096639195006983</v>
+        <v>-0.1096651483329406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3193451411898975</v>
+        <v>-0.3193446329637279</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1036790071198187</v>
+        <v>-0.1036926138894342</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01234068078596404</v>
+        <v>0.01232275203338851</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06578680099202693</v>
+        <v>-0.06574761415020311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1785392150676615</v>
+        <v>0.178547202690209</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2026567540346981</v>
+        <v>-0.2026682222244168</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2269829521610084</v>
+        <v>-0.2269482232632632</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1142139773657081</v>
+        <v>-0.1140534556231867</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.05003981524951013</v>
+        <v>-0.05002055857120786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07877312651142712</v>
+        <v>0.07893168194481018</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2393125682504539</v>
+        <v>0.2394184131759246</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1516709708631892</v>
+        <v>-0.1516319815592767</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05748294668211588</v>
+        <v>0.0575647103560713</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05546366373764739</v>
+        <v>-0.05494209222014342</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3230830635288741</v>
+        <v>-0.3230809581547338</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0511063981890348</v>
+        <v>-0.05113990405569698</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.331089797631131</v>
+        <v>-0.3310883313074113</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2417226331508232</v>
+        <v>-0.2417254208296967</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06578680099202693</v>
+        <v>-0.06574761415020311</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1760018636896864</v>
+        <v>0.1760051942293505</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3160445326223858</v>
+        <v>-0.3160482570070118</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04776706921303474</v>
+        <v>-0.04776509861757451</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05405410582917378</v>
+        <v>-0.05401392641573503</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3781245141595357</v>
+        <v>-0.3781123445815138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1640667344532792</v>
+        <v>0.1642217392833232</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009567965510844725</v>
+        <v>0.009685747131647993</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07244235647918937</v>
+        <v>-0.07243245758366815</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08428649701634369</v>
+        <v>0.08433269964814762</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03096896805885952</v>
+        <v>0.03171935978213337</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0132862791052903</v>
+        <v>0.01328905412502056</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2753068058748052</v>
+        <v>0.2752932961176366</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.255029386532689</v>
+        <v>-0.2550368089498125</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.07805718404123538</v>
+        <v>-0.07806354154150265</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1785392150676615</v>
+        <v>0.178547202690209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1760018636896864</v>
+        <v>0.1760051942293505</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.170598388165687</v>
+        <v>-0.1706180393863492</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3084537094760239</v>
+        <v>-0.3084615293647944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2227308902053908</v>
+        <v>-0.222711655829972</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1510164920534643</v>
+        <v>-0.1510190192440616</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1723341028743562</v>
+        <v>0.1722280269852077</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0224161539687822</v>
+        <v>0.02232142777691698</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1320314360024553</v>
+        <v>-0.1320539880904305</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02679369239775177</v>
+        <v>-0.02688864209852886</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.05877291858802467</v>
+        <v>-0.05945352624930481</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07433727870149821</v>
+        <v>0.07432555495722369</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.05196491633604719</v>
+        <v>-0.05198952396925561</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07542813836845864</v>
+        <v>0.07542806459283666</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.07455814137305526</v>
+        <v>-0.07455940277080558</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2026567540346981</v>
+        <v>-0.2026682222244168</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3160445326223858</v>
+        <v>-0.3160482570070118</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.170598388165687</v>
+        <v>-0.1706180393863492</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03946996866744708</v>
+        <v>-0.03948438549367227</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08856571338470084</v>
+        <v>-0.08860094175861424</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09264214096545345</v>
+        <v>-0.09265424735895804</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1092412006967712</v>
+        <v>-0.1094009951677595</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2283464053761993</v>
+        <v>-0.2283435410905121</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08339974035614572</v>
+        <v>0.08337446638556215</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08062582437501674</v>
+        <v>0.08054140858834195</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08778274974033642</v>
+        <v>0.08709367179480748</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1428103345211953</v>
+        <v>0.1428074056941042</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2138761412485604</v>
+        <v>-0.2138931787372331</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.02684651374004561</v>
+        <v>-0.02684996797353705</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.04508095526637061</v>
+        <v>-0.04508331966969938</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2269829521610084</v>
+        <v>-0.2269482232632632</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04776706921303474</v>
+        <v>-0.04776509861757451</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3084537094760239</v>
+        <v>-0.3084615293647944</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03946996866744708</v>
+        <v>-0.03948438549367227</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2788345723295459</v>
+        <v>0.2788371812811268</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09093476949449807</v>
+        <v>0.09093099774227098</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08463282091520734</v>
+        <v>-0.08450694487411456</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2056506966268644</v>
+        <v>-0.2054267870826997</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0363937100940993</v>
+        <v>-0.03637329299347228</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3015140425586836</v>
+        <v>-0.3014917714728322</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0326364474859536</v>
+        <v>-0.03179839919891501</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2452135479225645</v>
+        <v>-0.2452197395316884</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.08577513367168466</v>
+        <v>-0.0857951306035323</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.04727185076144911</v>
+        <v>-0.04729886021489226</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1499586067160359</v>
+        <v>-0.1499654042051256</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1142139773657081</v>
+        <v>-0.1140534556231867</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05405410582917378</v>
+        <v>-0.05401392641573503</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2227308902053908</v>
+        <v>-0.222711655829972</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08856571338470084</v>
+        <v>-0.08860094175861424</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2788345723295459</v>
+        <v>0.2788371812811268</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1493380521294727</v>
+        <v>-0.1493278868830226</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1753165760203162</v>
+        <v>-0.1748862623382345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2071447361832716</v>
+        <v>0.2075917649440903</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04254259850051654</v>
+        <v>-0.04251078395474015</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3745354334811894</v>
+        <v>-0.3743578348325354</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1858242244533122</v>
+        <v>0.1880811377806086</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1367996617520973</v>
+        <v>-0.1368264945330569</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0900453973643342</v>
+        <v>-0.09009036705947331</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02377053359026614</v>
+        <v>0.02376324638262087</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1114870266090247</v>
+        <v>0.111478058465224</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.05003981524951013</v>
+        <v>-0.05002055857120786</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3781245141595357</v>
+        <v>-0.3781123445815138</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1510164920534643</v>
+        <v>-0.1510190192440616</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.09264214096545345</v>
+        <v>-0.09265424735895804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09093476949449807</v>
+        <v>0.09093099774227098</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1493380521294727</v>
+        <v>-0.1493278868830226</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0989770011661326</v>
+        <v>0.09883082973761856</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.041651097361589</v>
+        <v>-0.04174660069819837</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04012001451470225</v>
+        <v>0.04011246558903302</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2065679647554099</v>
+        <v>-0.2066816690792193</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1996391652317889</v>
+        <v>-0.2004265540729127</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1058353326296024</v>
+        <v>-0.1058396420157976</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1461943316544137</v>
+        <v>-0.1462153886320437</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1225880484765356</v>
+        <v>0.1225047075877247</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2443402950117502</v>
+        <v>-0.2444970228166385</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07877312651142712</v>
+        <v>0.07893168194481018</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1640667344532792</v>
+        <v>0.1642217392833232</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1723341028743562</v>
+        <v>0.1722280269852077</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1092412006967712</v>
+        <v>-0.1094009951677595</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08463282091520734</v>
+        <v>-0.08450694487411456</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1753165760203162</v>
+        <v>-0.1748862623382345</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0989770011661326</v>
+        <v>0.09883082973761856</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1791510383185879</v>
+        <v>-0.1786833026508394</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.135853702062599</v>
+        <v>-0.1360722633625022</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1044035053771086</v>
+        <v>-0.1047745510758138</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2280967778745013</v>
+        <v>-0.2288438933218795</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2127925109409048</v>
+        <v>-0.2129852147301158</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08807077574002714</v>
+        <v>0.08796580053897103</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01712310662967702</v>
+        <v>-0.017206840120118</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07431393497876562</v>
+        <v>0.0741899723638027</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2393125682504539</v>
+        <v>0.2394184131759246</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009567965510844725</v>
+        <v>0.009685747131647993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0224161539687822</v>
+        <v>0.02232142777691698</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2283464053761993</v>
+        <v>-0.2283435410905121</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2056506966268644</v>
+        <v>-0.2054267870826997</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2071447361832716</v>
+        <v>0.2075917649440903</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.041651097361589</v>
+        <v>-0.04174660069819837</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1791510383185879</v>
+        <v>-0.1786833026508394</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06893924628442921</v>
+        <v>-0.06893997934291916</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04316120531137765</v>
+        <v>0.04329951486942914</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.11944139131725</v>
+        <v>-0.1162562195279469</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1961945947344522</v>
+        <v>-0.1962118513413593</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2873784801125753</v>
+        <v>-0.2873423660309426</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.07721829699917829</v>
+        <v>-0.07723501618661995</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1943296300502239</v>
+        <v>-0.194346715167301</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1516709708631892</v>
+        <v>-0.1516319815592767</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.07244235647918937</v>
+        <v>-0.07243245758366815</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1320314360024553</v>
+        <v>-0.1320539880904305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08339974035614572</v>
+        <v>0.08337446638556215</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0363937100940993</v>
+        <v>-0.03637329299347228</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04254259850051654</v>
+        <v>-0.04251078395474015</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04012001451470225</v>
+        <v>0.04011246558903302</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.135853702062599</v>
+        <v>-0.1360722633625022</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.06893924628442921</v>
+        <v>-0.06893997934291916</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.00335998864562518</v>
+        <v>0.00322130991802099</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1047634765795678</v>
+        <v>-0.1053255150930667</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.04995173120586962</v>
+        <v>-0.04997965481845353</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1150540772897141</v>
+        <v>-0.1150915291895788</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0614084395377903</v>
+        <v>-0.06147912687081618</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04310953272963792</v>
+        <v>0.04306455602606929</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05748294668211588</v>
+        <v>0.0575647103560713</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08428649701634369</v>
+        <v>0.08433269964814762</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02679369239775177</v>
+        <v>-0.02688864209852886</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08062582437501674</v>
+        <v>0.08054140858834195</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3015140425586836</v>
+        <v>-0.3014917714728322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3745354334811894</v>
+        <v>-0.3743578348325354</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2065679647554099</v>
+        <v>-0.2066816690792193</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1044035053771086</v>
+        <v>-0.1047745510758138</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04316120531137765</v>
+        <v>0.04329951486942914</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00335998864562518</v>
+        <v>0.00322130991802099</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.02755315356094067</v>
+        <v>-0.02834854872429162</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.009802906763255119</v>
+        <v>-0.009907069866554256</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1228143988473686</v>
+        <v>0.1227391512830113</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.06651761356820789</v>
+        <v>-0.0670025133674968</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.05767715707518035</v>
+        <v>-0.05820917583237969</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.05546366373764739</v>
+        <v>-0.05494209222014342</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03096896805885952</v>
+        <v>0.03171935978213337</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05877291858802467</v>
+        <v>-0.05945352624930481</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08778274974033642</v>
+        <v>0.08709367179480748</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0326364474859536</v>
+        <v>-0.03179839919891501</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1858242244533122</v>
+        <v>0.1880811377806086</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1996391652317889</v>
+        <v>-0.2004265540729127</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2280967778745013</v>
+        <v>-0.2288438933218795</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.11944139131725</v>
+        <v>-0.1162562195279469</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1047634765795678</v>
+        <v>-0.1053255150930667</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02755315356094067</v>
+        <v>-0.02834854872429162</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.09665459430950893</v>
+        <v>0.09590170272743821</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06347384352519776</v>
+        <v>0.06294665238404769</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1678714244500708</v>
+        <v>-0.1678669812375583</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1096639195006983</v>
+        <v>-0.1096651483329406</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3230830635288741</v>
+        <v>-0.3230809581547338</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0132862791052903</v>
+        <v>0.01328905412502056</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07433727870149821</v>
+        <v>0.07432555495722369</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1428103345211953</v>
+        <v>0.1428074056941042</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2452135479225645</v>
+        <v>-0.2452197395316884</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1367996617520973</v>
+        <v>-0.1368264945330569</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1058353326296024</v>
+        <v>-0.1058396420157976</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2127925109409048</v>
+        <v>-0.2129852147301158</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1961945947344522</v>
+        <v>-0.1962118513413593</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04995173120586962</v>
+        <v>-0.04997965481845353</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.009802906763255119</v>
+        <v>-0.009907069866554256</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09665459430950893</v>
+        <v>0.09590170272743821</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1243733342642975</v>
+        <v>0.1243667989543867</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2244993377801551</v>
+        <v>-0.2245020759487839</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3193451411898975</v>
+        <v>-0.3193446329637279</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0511063981890348</v>
+        <v>-0.05113990405569698</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2753068058748052</v>
+        <v>0.2752932961176366</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05196491633604719</v>
+        <v>-0.05198952396925561</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2138761412485604</v>
+        <v>-0.2138931787372331</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08577513367168466</v>
+        <v>-0.0857951306035323</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0900453973643342</v>
+        <v>-0.09009036705947331</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1461943316544137</v>
+        <v>-0.1462153886320437</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08807077574002714</v>
+        <v>0.08796580053897103</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2873784801125753</v>
+        <v>-0.2873423660309426</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1150540772897141</v>
+        <v>-0.1150915291895788</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1228143988473686</v>
+        <v>0.1227391512830113</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06347384352519776</v>
+        <v>0.06294665238404769</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1243733342642975</v>
+        <v>0.1243667989543867</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
